--- a/workshop_registration_form_templates/019_cross_functional_management_workshop_registration_form--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/019_cross_functional_management_workshop_registration_form--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_a</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_b</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_c</t>
+          <t>option c</t>
         </is>
       </c>
     </row>
